--- a/ws-subprg/ws_subprgList_protocolCore.xlsx
+++ b/ws-subprg/ws_subprgList_protocolCore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcorbara\Documents\ArgoX3_API_Mobile_CORE\ws-subprg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C89076-92EA-4AFF-87C6-18754D7947E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62486AFB-194D-40C1-876B-172D6DCFBF0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sottoprogramma" sheetId="1" r:id="rId1"/>
@@ -579,7 +579,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -692,10 +692,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -977,18 +973,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="20.42578125" customWidth="1"/>
     <col min="2" max="2" width="33" customWidth="1"/>
-    <col min="3" max="3" width="64.88671875" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" customWidth="1"/>
-    <col min="8" max="8" width="27.5546875" customWidth="1"/>
+    <col min="3" max="3" width="64.85546875" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" customWidth="1"/>
+    <col min="8" max="8" width="27.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1017,7 +1013,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1027,7 +1023,7 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="33" t="s">
         <v>7</v>
       </c>
@@ -1053,7 +1049,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="9"/>
@@ -1063,7 +1059,7 @@
       <c r="G4" s="9"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="33" t="s">
         <v>30</v>
       </c>
@@ -1090,7 +1086,7 @@
       </c>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="36"/>
       <c r="B6" s="8" t="s">
         <v>35</v>
@@ -1114,7 +1110,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="36"/>
       <c r="B7" s="8" t="s">
         <v>38</v>
@@ -1138,7 +1134,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="36"/>
       <c r="B8" s="8" t="s">
         <v>40</v>
@@ -1162,7 +1158,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="36"/>
       <c r="B9" s="8" t="s">
         <v>57</v>
@@ -1186,7 +1182,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="36"/>
       <c r="B10" s="8" t="s">
         <v>96</v>
@@ -1211,7 +1207,7 @@
       </c>
       <c r="I10" s="39"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="36"/>
       <c r="B11" s="8" t="s">
         <v>99</v>
@@ -1236,7 +1232,7 @@
       </c>
       <c r="I11" s="38"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="36"/>
       <c r="B12" s="8" t="s">
         <v>102</v>
@@ -1261,7 +1257,7 @@
       </c>
       <c r="I12" s="39"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="36"/>
       <c r="B13" s="8" t="s">
         <v>105</v>
@@ -1286,7 +1282,7 @@
       </c>
       <c r="I13" s="39"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="36"/>
       <c r="B14" s="8" t="s">
         <v>108</v>
@@ -1311,7 +1307,7 @@
       </c>
       <c r="I14" s="39"/>
     </row>
-    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="37"/>
       <c r="B15" s="22" t="s">
         <v>80</v>
@@ -1336,10 +1332,10 @@
       </c>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="33" t="s">
         <v>61</v>
       </c>
@@ -1365,7 +1361,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="36"/>
       <c r="B18" s="8" t="s">
         <v>64</v>
@@ -1389,7 +1385,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="36"/>
       <c r="B19" s="9" t="s">
         <v>66</v>
@@ -1413,7 +1409,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="36"/>
       <c r="B20" s="9" t="s">
         <v>68</v>
@@ -1437,7 +1433,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="37"/>
       <c r="B21" s="15" t="s">
         <v>70</v>
@@ -1461,8 +1457,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="32" t="s">
         <v>90</v>
       </c>
@@ -1496,16 +1492,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612F6477-338E-40CE-860A-6866966E781E}">
   <dimension ref="A1:G74"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.44140625" customWidth="1"/>
-    <col min="2" max="2" width="28.5546875" customWidth="1"/>
-    <col min="3" max="3" width="29.44140625" customWidth="1"/>
+    <col min="1" max="1" width="27.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="6" max="6" width="19.33203125" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>13</v>
       </c>
@@ -1525,8 +1521,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="32" t="s">
         <v>8</v>
       </c>
@@ -1546,7 +1542,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="12"/>
       <c r="B4" s="9" t="s">
         <v>18</v>
@@ -1564,7 +1560,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14"/>
       <c r="B5" s="15" t="s">
         <v>19</v>
@@ -1582,8 +1578,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="33" t="s">
         <v>31</v>
       </c>
@@ -1603,7 +1599,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="21"/>
       <c r="B8" s="22" t="s">
         <v>46</v>
@@ -1621,10 +1617,10 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="33" t="s">
         <v>35</v>
       </c>
@@ -1644,7 +1640,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="23"/>
       <c r="B11" s="8" t="s">
         <v>50</v>
@@ -1662,7 +1658,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="21"/>
       <c r="B12" s="22" t="s">
         <v>46</v>
@@ -1680,10 +1676,10 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
     </row>
-    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="33" t="s">
         <v>38</v>
       </c>
@@ -1704,7 +1700,7 @@
       </c>
       <c r="G14" s="9"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="23"/>
       <c r="B15" s="8" t="s">
         <v>45</v>
@@ -1723,7 +1719,7 @@
       </c>
       <c r="G15" s="9"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="23"/>
       <c r="B16" s="8" t="s">
         <v>51</v>
@@ -1742,7 +1738,7 @@
       </c>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="23"/>
       <c r="B17" s="8" t="s">
         <v>52</v>
@@ -1761,7 +1757,7 @@
       </c>
       <c r="G17" s="9"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="23"/>
       <c r="B18" s="8" t="s">
         <v>50</v>
@@ -1780,7 +1776,7 @@
       </c>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="23"/>
       <c r="B19" s="8" t="s">
         <v>53</v>
@@ -1799,7 +1795,7 @@
       </c>
       <c r="G19" s="9"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="23"/>
       <c r="B20" s="8" t="s">
         <v>54</v>
@@ -1818,7 +1814,7 @@
       </c>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="21"/>
       <c r="B21" s="22" t="s">
         <v>46</v>
@@ -1837,11 +1833,11 @@
       </c>
       <c r="G21" s="9"/>
     </row>
-    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
     </row>
-    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="33" t="s">
         <v>40</v>
       </c>
@@ -1861,7 +1857,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="21"/>
       <c r="B24" s="22" t="s">
         <v>46</v>
@@ -1879,10 +1875,10 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>
     </row>
-    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="33" t="s">
         <v>57</v>
       </c>
@@ -1902,7 +1898,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="21"/>
       <c r="B27" s="22" t="s">
         <v>46</v>
@@ -1920,7 +1916,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="9"/>
@@ -1928,7 +1924,7 @@
       <c r="E28" s="9"/>
       <c r="F28" s="8"/>
     </row>
-    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="33" t="s">
         <v>96</v>
       </c>
@@ -1948,7 +1944,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="21"/>
       <c r="B30" s="22" t="s">
         <v>46</v>
@@ -1966,7 +1962,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="9"/>
@@ -1974,7 +1970,7 @@
       <c r="E31" s="9"/>
       <c r="F31" s="8"/>
     </row>
-    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="33" t="s">
         <v>99</v>
       </c>
@@ -1994,7 +1990,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="21"/>
       <c r="B33" s="22" t="s">
         <v>46</v>
@@ -2012,7 +2008,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="9"/>
@@ -2020,7 +2016,7 @@
       <c r="E34" s="9"/>
       <c r="F34" s="8"/>
     </row>
-    <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="33" t="s">
         <v>102</v>
       </c>
@@ -2040,7 +2036,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="21"/>
       <c r="B36" s="22" t="s">
         <v>46</v>
@@ -2058,7 +2054,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="9"/>
@@ -2066,7 +2062,7 @@
       <c r="E37" s="9"/>
       <c r="F37" s="8"/>
     </row>
-    <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="33" t="s">
         <v>105</v>
       </c>
@@ -2086,7 +2082,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="23"/>
       <c r="B39" s="8" t="s">
         <v>111</v>
@@ -2104,7 +2100,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="23"/>
       <c r="B40" s="8" t="s">
         <v>112</v>
@@ -2122,7 +2118,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="21"/>
       <c r="B41" s="22" t="s">
         <v>46</v>
@@ -2140,7 +2136,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="9"/>
@@ -2148,7 +2144,7 @@
       <c r="E42" s="9"/>
       <c r="F42" s="8"/>
     </row>
-    <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="33" t="s">
         <v>108</v>
       </c>
@@ -2168,7 +2164,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="23"/>
       <c r="B44" s="8" t="s">
         <v>113</v>
@@ -2186,7 +2182,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="23"/>
       <c r="B45" s="8" t="s">
         <v>114</v>
@@ -2204,7 +2200,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="21"/>
       <c r="B46" s="22" t="s">
         <v>46</v>
@@ -2222,7 +2218,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="9"/>
@@ -2230,7 +2226,7 @@
       <c r="E47" s="9"/>
       <c r="F47" s="8"/>
     </row>
-    <row r="48" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="33" t="s">
         <v>80</v>
       </c>
@@ -2250,7 +2246,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="23"/>
       <c r="B49" s="8" t="s">
         <v>83</v>
@@ -2268,7 +2264,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="23"/>
       <c r="B50" s="8" t="s">
         <v>84</v>
@@ -2286,7 +2282,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="23"/>
       <c r="B51" s="8" t="s">
         <v>85</v>
@@ -2304,7 +2300,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="23"/>
       <c r="B52" s="8" t="s">
         <v>86</v>
@@ -2322,7 +2318,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="23"/>
       <c r="B53" s="8" t="s">
         <v>87</v>
@@ -2340,7 +2336,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="23"/>
       <c r="B54" s="8" t="s">
         <v>88</v>
@@ -2358,7 +2354,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="21"/>
       <c r="B55" s="22" t="s">
         <v>46</v>
@@ -2376,7 +2372,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="9"/>
@@ -2384,7 +2380,7 @@
       <c r="E56" s="9"/>
       <c r="F56" s="8"/>
     </row>
-    <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="32" t="s">
         <v>62</v>
       </c>
@@ -2404,7 +2400,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="30"/>
       <c r="B58" s="8" t="s">
         <v>73</v>
@@ -2422,7 +2418,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="31"/>
       <c r="B59" s="22" t="s">
         <v>46</v>
@@ -2440,8 +2436,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="61" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="61" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="33" t="s">
         <v>64</v>
       </c>
@@ -2461,7 +2457,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="21"/>
       <c r="B62" s="22" t="s">
         <v>46</v>
@@ -2479,8 +2475,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="64" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="33" t="s">
         <v>66</v>
       </c>
@@ -2500,7 +2496,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="21"/>
       <c r="B65" s="22" t="s">
         <v>46</v>
@@ -2518,8 +2514,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="67" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="67" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="33" t="s">
         <v>68</v>
       </c>
@@ -2539,7 +2535,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="21"/>
       <c r="B68" s="22" t="s">
         <v>46</v>
@@ -2557,8 +2553,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="70" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="33" t="s">
         <v>70</v>
       </c>
@@ -2578,7 +2574,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="21"/>
       <c r="B71" s="22" t="s">
         <v>46</v>
@@ -2596,8 +2592,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="73" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="32" t="s">
         <v>91</v>
       </c>
@@ -2617,7 +2613,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="31"/>
       <c r="B74" s="22" t="s">
         <v>46</v>
@@ -2643,16 +2639,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{307633E0-95BB-4101-8F21-8B6A9E0EBAC5}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.6640625" customWidth="1"/>
-    <col min="2" max="2" width="30.5546875" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" customWidth="1"/>
-    <col min="4" max="4" width="45.44140625" customWidth="1"/>
-    <col min="5" max="5" width="23.5546875" customWidth="1"/>
+    <col min="1" max="1" width="29.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.5703125" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" customWidth="1"/>
+    <col min="4" max="4" width="45.42578125" customWidth="1"/>
+    <col min="5" max="5" width="23.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>56</v>
       </c>
@@ -2672,14 +2668,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="33" t="s">
         <v>7</v>
       </c>
@@ -2696,14 +2692,14 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
     </row>
-    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="33" t="s">
         <v>30</v>
       </c>
@@ -2720,7 +2716,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="23"/>
       <c r="B6" s="8" t="s">
         <v>35</v>
@@ -2735,7 +2731,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="23"/>
       <c r="B7" s="8" t="s">
         <v>38</v>
@@ -2750,7 +2746,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="23"/>
       <c r="B8" s="8" t="s">
         <v>40</v>
@@ -2765,7 +2761,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="23"/>
       <c r="B9" s="8" t="s">
         <v>57</v>
@@ -2780,7 +2776,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="23"/>
       <c r="B10" s="8" t="s">
         <v>96</v>
@@ -2794,9 +2790,9 @@
       <c r="E10" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="40"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="23"/>
       <c r="B11" s="8" t="s">
         <v>99</v>
@@ -2810,9 +2806,8 @@
       <c r="E11" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="41"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="23"/>
       <c r="B12" s="8" t="s">
         <v>102</v>
@@ -2826,9 +2821,8 @@
       <c r="E12" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="41"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="23"/>
       <c r="B13" s="8" t="s">
         <v>105</v>
@@ -2842,9 +2836,8 @@
       <c r="E13" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="41"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="23"/>
       <c r="B14" s="8" t="s">
         <v>108</v>
@@ -2858,9 +2851,8 @@
       <c r="E14" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="41"/>
-    </row>
-    <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="21"/>
       <c r="B15" s="22" t="s">
         <v>80</v>
@@ -2875,8 +2867,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="32" t="s">
         <v>61</v>
       </c>
@@ -2893,7 +2885,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="30"/>
       <c r="B18" s="8" t="s">
         <v>64</v>
@@ -2908,7 +2900,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="30"/>
       <c r="B19" s="9" t="s">
         <v>66</v>
@@ -2923,7 +2915,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="30"/>
       <c r="B20" s="9" t="s">
         <v>68</v>
@@ -2938,7 +2930,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="31"/>
       <c r="B21" s="15" t="s">
         <v>70</v>
@@ -2953,8 +2945,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="32" t="s">
         <v>90</v>
       </c>
@@ -2979,15 +2971,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9BC2AFE-8505-46FC-A172-307AD377E7A4}">
   <dimension ref="A1:G51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
-    <col min="2" max="2" width="34.88671875" customWidth="1"/>
-    <col min="3" max="3" width="23.5546875" customWidth="1"/>
-    <col min="5" max="5" width="18.33203125" customWidth="1"/>
+    <col min="2" max="2" width="34.85546875" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>25</v>
       </c>
@@ -3007,8 +2999,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="32" t="s">
         <v>8</v>
       </c>
@@ -3028,7 +3020,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="12"/>
       <c r="B4" s="9" t="s">
         <v>18</v>
@@ -3046,7 +3038,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14"/>
       <c r="B5" s="15" t="s">
         <v>19</v>
@@ -3064,8 +3056,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="33" t="s">
         <v>31</v>
       </c>
@@ -3085,7 +3077,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="21"/>
       <c r="B8" s="22" t="s">
         <v>46</v>
@@ -3103,8 +3095,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="33" t="s">
         <v>38</v>
       </c>
@@ -3124,7 +3116,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="23"/>
       <c r="B11" s="8" t="s">
         <v>45</v>
@@ -3142,7 +3134,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="23"/>
       <c r="B12" s="8" t="s">
         <v>51</v>
@@ -3160,7 +3152,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="23"/>
       <c r="B13" s="8" t="s">
         <v>52</v>
@@ -3178,7 +3170,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="23"/>
       <c r="B14" s="8" t="s">
         <v>50</v>
@@ -3196,7 +3188,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="23"/>
       <c r="B15" s="8" t="s">
         <v>53</v>
@@ -3214,7 +3206,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="23"/>
       <c r="B16" s="8" t="s">
         <v>54</v>
@@ -3232,7 +3224,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="21"/>
       <c r="B17" s="22" t="s">
         <v>46</v>
@@ -3250,8 +3242,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="33" t="s">
         <v>40</v>
       </c>
@@ -3271,7 +3263,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="21"/>
       <c r="B20" s="22" t="s">
         <v>46</v>
@@ -3289,10 +3281,10 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>
     </row>
-    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="33" t="s">
         <v>42</v>
       </c>
@@ -3312,7 +3304,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="21"/>
       <c r="B23" s="22" t="s">
         <v>46</v>
@@ -3330,7 +3322,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="9"/>
@@ -3338,7 +3330,7 @@
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
     </row>
-    <row r="25" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="33" t="s">
         <v>80</v>
       </c>
@@ -3358,7 +3350,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="23"/>
       <c r="B26" s="8" t="s">
         <v>83</v>
@@ -3376,7 +3368,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="23"/>
       <c r="B27" s="8" t="s">
         <v>84</v>
@@ -3394,7 +3386,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="23"/>
       <c r="B28" s="8" t="s">
         <v>85</v>
@@ -3412,7 +3404,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="23"/>
       <c r="B29" s="8" t="s">
         <v>86</v>
@@ -3430,7 +3422,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="23"/>
       <c r="B30" s="8" t="s">
         <v>87</v>
@@ -3448,7 +3440,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="23"/>
       <c r="B31" s="8" t="s">
         <v>88</v>
@@ -3466,7 +3458,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="21"/>
       <c r="B32" s="22" t="s">
         <v>46</v>
@@ -3484,7 +3476,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="9"/>
@@ -3492,7 +3484,7 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="32" t="s">
         <v>62</v>
       </c>
@@ -3513,7 +3505,7 @@
       </c>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="30"/>
       <c r="B35" s="8" t="s">
         <v>73</v>
@@ -3531,7 +3523,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="31"/>
       <c r="B36" s="22" t="s">
         <v>46</v>
@@ -3549,10 +3541,10 @@
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G37" s="9"/>
     </row>
-    <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="33" t="s">
         <v>64</v>
       </c>
@@ -3572,7 +3564,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="21"/>
       <c r="B39" s="22" t="s">
         <v>46</v>
@@ -3590,8 +3582,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="41" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="33" t="s">
         <v>66</v>
       </c>
@@ -3611,7 +3603,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="21"/>
       <c r="B42" s="22" t="s">
         <v>46</v>
@@ -3629,8 +3621,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="33" t="s">
         <v>68</v>
       </c>
@@ -3650,7 +3642,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="21"/>
       <c r="B45" s="22" t="s">
         <v>46</v>
@@ -3668,8 +3660,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="33" t="s">
         <v>70</v>
       </c>
@@ -3689,7 +3681,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="21"/>
       <c r="B48" s="22" t="s">
         <v>46</v>
@@ -3707,8 +3699,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="50" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="50" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="32" t="s">
         <v>91</v>
       </c>
@@ -3728,7 +3720,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="31"/>
       <c r="B51" s="22" t="s">
         <v>46</v>

--- a/ws-subprg/ws_subprgList_protocolCore.xlsx
+++ b/ws-subprg/ws_subprgList_protocolCore.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcorbara\Documents\ArgoX3_API_Mobile_CORE\ws-subprg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62486AFB-194D-40C1-876B-172D6DCFBF0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B316CB08-9CB7-4491-998A-03103E3B1644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="117">
   <si>
     <t>File</t>
   </si>
@@ -373,6 +373,12 @@
   </si>
   <si>
     <t>YNEWSALT</t>
+  </si>
+  <si>
+    <t>YAX3MDEMOLIB</t>
+  </si>
+  <si>
+    <t>YSAVEINFO</t>
   </si>
 </sst>
 </file>
@@ -579,7 +585,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -692,6 +698,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -2638,7 +2645,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{307633E0-95BB-4101-8F21-8B6A9E0EBAC5}">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.7109375" customWidth="1"/>
@@ -2960,6 +2967,20 @@
         <v>94</v>
       </c>
       <c r="E23" s="34" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="34" t="s">
         <v>29</v>
       </c>
     </row>

--- a/ws-subprg/ws_subprgList_protocolCore.xlsx
+++ b/ws-subprg/ws_subprgList_protocolCore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcorbara\Documents\ArgoX3_API_Mobile_CORE\ws-subprg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B316CB08-9CB7-4491-998A-03103E3B1644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8E246F-0EE2-4CA3-B7A8-4867B50D8D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sottoprogramma" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="119">
   <si>
     <t>File</t>
   </si>
@@ -379,6 +379,12 @@
   </si>
   <si>
     <t>YSAVEINFO</t>
+  </si>
+  <si>
+    <t>Codice Tipo per Patch</t>
+  </si>
+  <si>
+    <t>ASU</t>
   </si>
 </sst>
 </file>
@@ -408,7 +414,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -418,12 +424,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -585,7 +585,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -694,11 +694,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -979,48 +988,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.42578125" customWidth="1"/>
     <col min="2" max="2" width="33" customWidth="1"/>
-    <col min="3" max="3" width="64.85546875" customWidth="1"/>
+    <col min="3" max="3" width="69.28515625" customWidth="1"/>
     <col min="4" max="4" width="12.42578125" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" customWidth="1"/>
     <col min="7" max="7" width="10.7109375" customWidth="1"/>
     <col min="8" max="8" width="27.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:10" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="B1" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="35" t="s">
+      <c r="I1" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="J1" s="35" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1029,8 +1041,9 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="33" t="s">
         <v>7</v>
       </c>
@@ -1055,8 +1068,11 @@
       <c r="H3" s="29" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I3" s="39" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="9"/>
@@ -1065,8 +1081,9 @@
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
       <c r="H4" s="8"/>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I4" s="8"/>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="33" t="s">
         <v>30</v>
       </c>
@@ -1091,9 +1108,12 @@
       <c r="H5" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="9"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I5" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="J5" s="9"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="36"/>
       <c r="B6" s="8" t="s">
         <v>35</v>
@@ -1116,8 +1136,11 @@
       <c r="H6" s="13" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I6" s="39" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="36"/>
       <c r="B7" s="8" t="s">
         <v>38</v>
@@ -1140,8 +1163,11 @@
       <c r="H7" s="13" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I7" s="39" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="36"/>
       <c r="B8" s="8" t="s">
         <v>40</v>
@@ -1164,8 +1190,11 @@
       <c r="H8" s="13" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I8" s="39" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="36"/>
       <c r="B9" s="8" t="s">
         <v>57</v>
@@ -1188,8 +1217,11 @@
       <c r="H9" s="13" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I9" s="39" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="36"/>
       <c r="B10" s="8" t="s">
         <v>96</v>
@@ -1212,9 +1244,12 @@
       <c r="H10" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="I10" s="39"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I10" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="J10" s="41"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="36"/>
       <c r="B11" s="8" t="s">
         <v>99</v>
@@ -1237,9 +1272,12 @@
       <c r="H11" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="I11" s="38"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I11" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="J11" s="42"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="36"/>
       <c r="B12" s="8" t="s">
         <v>102</v>
@@ -1262,9 +1300,12 @@
       <c r="H12" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="I12" s="39"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I12" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="J12" s="41"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="36"/>
       <c r="B13" s="8" t="s">
         <v>105</v>
@@ -1287,9 +1328,12 @@
       <c r="H13" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="I13" s="39"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I13" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="J13" s="41"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="36"/>
       <c r="B14" s="8" t="s">
         <v>108</v>
@@ -1312,9 +1356,12 @@
       <c r="H14" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="I14" s="39"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I14" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="J14" s="41"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="37"/>
       <c r="B15" s="22" t="s">
         <v>80</v>
@@ -1337,12 +1384,15 @@
       <c r="H15" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="I15" s="9"/>
-    </row>
-    <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I16" s="9"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I15" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="J15" s="9"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J16" s="9"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="33" t="s">
         <v>61</v>
       </c>
@@ -1367,8 +1417,11 @@
       <c r="H17" s="11" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I17" s="39" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="36"/>
       <c r="B18" s="8" t="s">
         <v>64</v>
@@ -1391,8 +1444,11 @@
       <c r="H18" s="13" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I18" s="39" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="36"/>
       <c r="B19" s="9" t="s">
         <v>66</v>
@@ -1415,8 +1471,11 @@
       <c r="H19" s="18" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I19" s="39" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="36"/>
       <c r="B20" s="9" t="s">
         <v>68</v>
@@ -1439,8 +1498,11 @@
       <c r="H20" s="18" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I20" s="39" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="37"/>
       <c r="B21" s="15" t="s">
         <v>70</v>
@@ -1463,9 +1525,12 @@
       <c r="H21" s="19" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I21" s="39" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="32" t="s">
         <v>90</v>
       </c>
@@ -1489,6 +1554,9 @@
       </c>
       <c r="H23" s="34" t="s">
         <v>91</v>
+      </c>
+      <c r="I23" s="40" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -2978,8 +3046,8 @@
       <c r="B25" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
       <c r="E25" s="34" t="s">
         <v>29</v>
       </c>
